--- a/artfynd/A 57463-2025 artfynd.xlsx
+++ b/artfynd/A 57463-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>6624983</v>
+        <v>178901</v>
       </c>
       <c r="B2" t="n">
-        <v>85200</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87233</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>248956</v>
+        <v>442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Bullspindling</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius corrosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>737956.3927384757</v>
+        <v>738005</v>
       </c>
       <c r="R2" t="n">
-        <v>6415617.319902884</v>
+        <v>6415594</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -757,19 +752,9 @@
           <t>2011-09-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2011-09-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104073069</v>
+        <v>104073068</v>
       </c>
       <c r="B3" t="n">
-        <v>85278</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +792,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6003295</v>
+        <v>3712</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +816,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>738022.9849394629</v>
+        <v>738140</v>
       </c>
       <c r="R3" t="n">
-        <v>6415658.110947064</v>
+        <v>6415639</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,19 +849,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,16 +890,11 @@
         <v>104073071</v>
       </c>
       <c r="B4" t="n">
-        <v>85105</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87170</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -957,10 +922,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>738033.905931105</v>
+        <v>738034</v>
       </c>
       <c r="R4" t="n">
-        <v>6415636.332838478</v>
+        <v>6415636</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -990,19 +955,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,12 +996,7 @@
         <v>104073070</v>
       </c>
       <c r="B5" t="n">
-        <v>85224</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87291</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1078,10 +1028,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>738028.9154040351</v>
+        <v>738029</v>
       </c>
       <c r="R5" t="n">
-        <v>6415648.317672097</v>
+        <v>6415648</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,19 +1061,9 @@
           <t>2022-10-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-10-12</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1152,6 +1092,324 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>6624983</v>
+      </c>
+      <c r="B6" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rute, öster ale, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>737956</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6415617</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2011-09-28</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2011-09-28</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åke Edvinsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104073069</v>
+      </c>
+      <c r="B7" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sildnäs NV, Alby 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>738023</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6415658</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Inventering av kalkbarrskog på Gotland 2022</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104073072</v>
+      </c>
+      <c r="B8" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sildnäs NV, Alby 1:15, Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>738039</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6415608</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Rute</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-10-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Jan  Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>

--- a/artfynd/A 57463-2025 artfynd.xlsx
+++ b/artfynd/A 57463-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/178901</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073068</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073071</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073070</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1202,6 +1227,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6624983</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1308,6 +1338,11 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073069</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1414,8 +1449,22 @@
           <t>Inventering av kalkbarrskog på Gotland 2022</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104073072</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>